--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90171</v>
+        <v>90173</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90173</v>
+        <v>90174</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90174</v>
+        <v>90183</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90183</v>
+        <v>90190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90190</v>
+        <v>90192</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90208</v>
+        <v>90218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90218</v>
+        <v>90230</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 61186-2024 artfynd.xlsx
+++ b/artfynd/A 61186-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122031511</v>
       </c>
       <c r="B2" t="n">
-        <v>90230</v>
+        <v>90234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
